--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117477323</v>
+        <v>117477217</v>
       </c>
       <c r="B2" t="n">
-        <v>101000</v>
+        <v>56741</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117477110</v>
+        <v>117477088</v>
       </c>
       <c r="B3" t="n">
-        <v>100097</v>
+        <v>97859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +812,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117477234</v>
+        <v>117477323</v>
       </c>
       <c r="B4" t="n">
-        <v>56341</v>
+        <v>101000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +929,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117477217</v>
+        <v>117477234</v>
       </c>
       <c r="B5" t="n">
-        <v>56741</v>
+        <v>56341</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117477088</v>
+        <v>117477110</v>
       </c>
       <c r="B6" t="n">
-        <v>97859</v>
+        <v>100097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,27 +1167,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117477217</v>
+        <v>117477088</v>
       </c>
       <c r="B2" t="n">
-        <v>56741</v>
+        <v>97861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102954</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -796,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117477088</v>
+        <v>117477110</v>
       </c>
       <c r="B3" t="n">
-        <v>97859</v>
+        <v>100099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -916,7 +912,7 @@
         <v>117477323</v>
       </c>
       <c r="B4" t="n">
-        <v>101000</v>
+        <v>101002</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1151,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117477110</v>
+        <v>117477217</v>
       </c>
       <c r="B6" t="n">
-        <v>100097</v>
+        <v>56742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,27 +1163,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>102954</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,6 +1266,123 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117479512</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104839</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brödlösberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>508714</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6764897</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sofia Möller Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -1271,7 +1271,7 @@
         <v>117479512</v>
       </c>
       <c r="B7" t="n">
-        <v>104839</v>
+        <v>104846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1383,6 +1383,126 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120423086</v>
+      </c>
+      <c r="B8" t="n">
+        <v>42941</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källmyränget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>508813</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6764706</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Boda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120423086</v>
+        <v>120431664</v>
       </c>
       <c r="B8" t="n">
         <v>42941</v>

--- a/artfynd/A 60888-2023 artfynd.xlsx
+++ b/artfynd/A 60888-2023 artfynd.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120431664</v>
+        <v>120423086</v>
       </c>
       <c r="B8" t="n">
         <v>42941</v>
